--- a/data/raw/drug_plantations.xlsx
+++ b/data/raw/drug_plantations.xlsx
@@ -1,35 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="ClassifiedData" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data2Classify" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ClassifiedData" sheetId="1" r:id="rId1"/>
+    <sheet name="Data2Classify" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,80 +66,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -200,6 +151,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,6 +186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -268,20 +221,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -403,7022 +352,6786 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F301"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>BD1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>BD2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>BD3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>BD4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>DrugPlant</t>
-        </is>
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>BD1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>BD2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>BD3</v>
+      </c>
+      <c r="E1" t="str">
+        <v>BD4</v>
+      </c>
+      <c r="F1" t="str">
+        <v>DrugPlant</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>35.4</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>36.6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>14.55</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="str">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>23.9</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>51.6</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>7.94</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>20.7</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>50.8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>19</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>7.3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>20.2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>35.7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>14</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>12.35</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>21.8</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>56.5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>12.71</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>17.4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>45.1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>23</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>7.2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>21.1</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>43.7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>24</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>8.15</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>22.3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>49.8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>26</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>13.74</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>22</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>58.1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>12.19</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>23.3</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>37</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>19</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>13.15</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>23.6</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>47.5</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>7</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>7.87</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>19.5</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>41.4</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>18</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>12.47</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>21.1</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>55.7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>11.49</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>31.8</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>56.3</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>8.26</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>23.2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>46.9</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>18</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>8.35</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>21.1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>59.7</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>11</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>12.77</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>20.2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>56.4</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>23</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>6.8</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>15.8</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>49.1</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>16</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>9.27</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>30.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>47.1</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>10</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>15.12</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>32.4</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>30.4</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>16</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>14.41</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>20.3</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>48.2</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>21</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>12.32</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>26.7</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>51.8</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>11</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>5.72</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>19.6</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>49.9</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>18</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>10.04</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>18.9</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>56.3</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>22</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>14.75</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>17.4</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>52.2</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>10</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>10.83</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>15.8</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>52.6</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>11.44</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>24.9</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>32.7</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>22</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>11.08</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>22.5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>48.7</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>23</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>13.61</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>16.3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>44.5</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>13</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>11.14</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>25.7</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>58.4</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>12</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>15.4</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>26.8</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>39.1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>18</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>12.56</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>17.1</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>50.8</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>19</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>10.45</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>16.4</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>58.5</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>13.33</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>20.3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>54.6</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>14</v>
       </c>
-      <c r="E35" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35">
+        <v>9.96</v>
+      </c>
+      <c r="F35">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>23.5</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>40.1</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>8</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>10.49</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>17.6</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>54.5</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>19</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>10.79</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>17</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>55</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>16</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>5.92</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>19.4</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>48.7</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>13</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>9.57</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>21.2</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>53.3</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>18</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>11.73</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>17.8</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>50.7</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>12</v>
       </c>
-      <c r="E41" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="F41" t="n">
+      <c r="E41">
+        <v>8.78</v>
+      </c>
+      <c r="F41">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>18.7</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>40.3</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>8</v>
       </c>
-      <c r="E42" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="F42" t="n">
+      <c r="E42">
+        <v>9.89</v>
+      </c>
+      <c r="F42">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>19.1</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>46.1</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>17</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>9.92</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>21.7</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>42.1</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>13</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>10.05</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>19.3</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>45.9</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>24</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>12.01</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>23.8</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>45.8</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>14</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>10.61</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>1</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>26.3</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>57</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>18</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>11.06</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>17.9</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>51.9</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>8</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>9.67</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>27.8</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>39.4</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>8</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>13.15</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>1</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>21.5</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>59.5</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>24</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>10.17</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>15.5</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>51</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>5</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>11.88</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>15</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>52.5</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>5</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>12.03</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>18.2</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>44.7</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>9</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>8.92</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>22.7</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>48.5</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>6</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>9.59</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>17.7</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>57</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>12</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>7.85</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>17.4</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>55.2</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>20</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>6.35</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>8.4</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>48.7</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>8</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>12.38</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>18.4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>50.1</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>24</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>7.26</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>21.2</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>51.4</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>24</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>8.16</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>27.8</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>35.4</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>15</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>14.95</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>1</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>21.7</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>48.7</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>10</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>6.63</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>18.7</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>46.4</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>7</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>11.2</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>19.1</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>40.3</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>14</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>7.89</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>23.3</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>51.1</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>16</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>7.16</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>25.5</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>41</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>10</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>12.55</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>1</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>10.8</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>39.8</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>24</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>7.87</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>24.1</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>44.4</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>11</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>10.59</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>21.7</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>41.4</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>20</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>17.55</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>25.5</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>29.8</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>15</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>11.69</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>26.8</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>51.3</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>18</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>11.16</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>23</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>51.9</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>13</v>
       </c>
-      <c r="E71" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="F71" t="n">
+      <c r="E71">
+        <v>8.46</v>
+      </c>
+      <c r="F71">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>23.6</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>54.5</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>22</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>9.4</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>27.4</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>45.8</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>6</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>10.23</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>15.6</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>40</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>17</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>9.81</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>21</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>54.4</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>19</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>10.31</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>21</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>40.4</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>20</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>6.95</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>16.1</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>53.8</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>24</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>14.35</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>34</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>37.3</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>26</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>10.57</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>17.7</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>42.9</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>9</v>
       </c>
-      <c r="E79" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="F79" t="n">
+      <c r="E79">
+        <v>9.54</v>
+      </c>
+      <c r="F79">
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>23.1</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>44.1</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>15</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>15.97</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>1</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>27.1</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>49.9</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>12</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>12.03</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>1</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>30.1</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>40.9</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>10</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>16.52</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>1</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>17.6</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>48.3</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>20</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>6.36</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>17.6</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>38.2</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>23</v>
       </c>
-      <c r="E84" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="F84" t="n">
+      <c r="E84">
+        <v>8.03</v>
+      </c>
+      <c r="F84">
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>28</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>47.8</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>17</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>8</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>1</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>20.3</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>42.5</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>26</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>16.46</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>1</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>16.9</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>48.1</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>5</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>6.89</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>16.6</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>59.2</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>20</v>
       </c>
-      <c r="E88" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="F88" t="n">
+      <c r="E88">
+        <v>8.14</v>
+      </c>
+      <c r="F88">
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>18.3</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>39</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>5</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>11.78</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>19.4</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>46.5</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>17</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>10.72</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>27.4</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>50</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>24</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>12.52</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>23.6</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>47.9</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>12</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>11.47</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>26.1</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>24.9</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>22</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>16.08</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>1</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>19.1</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>52.4</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>20</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>8.65</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>23.5</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>49.8</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>15</v>
       </c>
-      <c r="E95" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="F95" t="n">
+      <c r="E95">
+        <v>9.63</v>
+      </c>
+      <c r="F95">
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>21.7</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>57.1</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>13</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>11.69</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>23.6</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>64.3</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>8</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>11.73</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>25.5</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>48.7</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>19</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>12.21</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>16</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>52.7</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>23</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>7.93</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>17</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>43.8</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>15</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>11.1</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>1</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>19.9</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>51.2</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>12</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>6.71</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>20.3</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>49</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>8</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>8.66</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>27.1</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>44.7</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>14</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>13.59</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>1</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>17.6</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>57.9</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>17</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>6.86</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>19.1</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>44.1</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>20</v>
       </c>
-      <c r="E105" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="F105" t="n">
+      <c r="E105">
+        <v>9.38</v>
+      </c>
+      <c r="F105">
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>22.2</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>63.3</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>23</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>11.42</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>28.5</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>45.5</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>24</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>16.31</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>1</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>25.3</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>52.1</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>15</v>
       </c>
-      <c r="E108" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="F108" t="n">
+      <c r="E108">
+        <v>8.37</v>
+      </c>
+      <c r="F108">
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>11.3</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>34.3</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>5</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>11.26</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>13.4</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110">
         <v>49.9</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>8</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>6.65</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>25.8</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111">
         <v>43.2</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>16</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>8.19</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>22.4</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>54</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>17</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>10.11</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>23.2</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>56.7</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>12</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>8.23</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>18.9</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>58</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>16</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>7.89</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>24.1</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>40.8</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>27</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>14.51</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>1</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>26.8</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>41.5</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>22</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>11.36</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>1</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>22.2</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>45.1</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>14</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>14.12</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>1</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118">
         <v>117</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>19.9</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>27.3</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>27</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>13.57</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>1</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119">
         <v>118</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>15.6</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>47</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>11</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>11.11</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120">
         <v>119</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>26.5</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120">
         <v>38.2</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120">
         <v>10</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>15.73</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>1</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121">
         <v>120</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>22.5</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121">
         <v>53.6</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121">
         <v>18</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>10.17</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>26.6</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122">
         <v>46.8</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122">
         <v>19</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>8.6</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>21.5</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123">
         <v>55.2</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123">
         <v>23</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>12.36</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>21.9</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124">
         <v>48.7</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124">
         <v>6</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>10.33</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125">
         <v>124</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>26.8</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125">
         <v>56</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125">
         <v>17</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>7.64</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>0</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126">
         <v>125</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>16.9</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126">
         <v>65.5</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126">
         <v>24</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>10.27</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>0</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127">
         <v>126</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>22.2</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127">
         <v>52.9</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127">
         <v>19</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>12.3</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>1</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128">
         <v>127</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128">
         <v>17.8</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128">
         <v>56.6</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128">
         <v>22</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128">
         <v>3.52</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129">
         <v>128</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129">
         <v>19.6</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129">
         <v>58</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129">
         <v>7</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129">
         <v>7.44</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>0</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130">
         <v>129</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130">
         <v>28.1</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130">
         <v>47.4</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130">
         <v>5</v>
       </c>
-      <c r="E130" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="F130" t="n">
+      <c r="E130">
+        <v>8.89</v>
+      </c>
+      <c r="F130">
         <v>0</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131">
         <v>130</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131">
         <v>18.6</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131">
         <v>44.6</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131">
         <v>10</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131">
         <v>8.69</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132">
         <v>131</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132">
         <v>25.2</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132">
         <v>44.1</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132">
         <v>23</v>
       </c>
-      <c r="E132" t="n">
+      <c r="E132">
         <v>5.99</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132">
         <v>0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133">
         <v>132</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133">
         <v>18.1</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133">
         <v>51.4</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133">
         <v>20</v>
       </c>
-      <c r="E133" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="F133" t="n">
+      <c r="E133">
+        <v>8.96</v>
+      </c>
+      <c r="F133">
         <v>0</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134">
         <v>133</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134">
         <v>22</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134">
         <v>60.3</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134">
         <v>19</v>
       </c>
-      <c r="E134" t="n">
+      <c r="E134">
         <v>10.9</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134">
         <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135">
         <v>134</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135">
         <v>22.7</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135">
         <v>44.9</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135">
         <v>7</v>
       </c>
-      <c r="E135" t="n">
+      <c r="E135">
         <v>6.98</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135">
         <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136">
         <v>135</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136">
         <v>28.1</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136">
         <v>45.3</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136">
         <v>26</v>
       </c>
-      <c r="E136" t="n">
+      <c r="E136">
         <v>14.47</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136">
         <v>1</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137">
         <v>136</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137">
         <v>23</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137">
         <v>41.3</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137">
         <v>23</v>
       </c>
-      <c r="E137" t="n">
+      <c r="E137">
         <v>4.77</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137">
         <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138">
         <v>137</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138">
         <v>17.2</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138">
         <v>41.5</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138">
         <v>12</v>
       </c>
-      <c r="E138" t="n">
+      <c r="E138">
         <v>11.1</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138">
         <v>0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139">
         <v>138</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139">
         <v>25.8</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139">
         <v>56</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139">
         <v>23</v>
       </c>
-      <c r="E139" t="n">
+      <c r="E139">
         <v>8.42</v>
       </c>
-      <c r="F139" t="n">
+      <c r="F139">
         <v>0</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140">
         <v>139</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140">
         <v>23.9</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140">
         <v>45.2</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140">
         <v>9</v>
       </c>
-      <c r="E140" t="n">
+      <c r="E140">
         <v>6.48</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140">
         <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141">
         <v>140</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141">
         <v>17.2</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141">
         <v>45</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141">
         <v>17</v>
       </c>
-      <c r="E141" t="n">
+      <c r="E141">
         <v>12.6</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F141">
         <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142">
         <v>141</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142">
         <v>22</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142">
         <v>63.8</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142">
         <v>15</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E142">
         <v>10.99</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142">
         <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143">
         <v>142</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143">
         <v>15.7</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143">
         <v>50.5</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143">
         <v>11</v>
       </c>
-      <c r="E143" t="n">
+      <c r="E143">
         <v>12.2</v>
       </c>
-      <c r="F143" t="n">
+      <c r="F143">
         <v>0</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144">
         <v>143</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144">
         <v>26.4</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144">
         <v>41.7</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144">
         <v>12</v>
       </c>
-      <c r="E144" t="n">
+      <c r="E144">
         <v>14.6</v>
       </c>
-      <c r="F144" t="n">
+      <c r="F144">
         <v>1</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145">
         <v>15.3</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145">
         <v>48.4</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145">
         <v>23</v>
       </c>
-      <c r="E145" t="n">
+      <c r="E145">
         <v>10.69</v>
       </c>
-      <c r="F145" t="n">
+      <c r="F145">
         <v>0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146">
         <v>22.9</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146">
         <v>52.9</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146">
         <v>21</v>
       </c>
-      <c r="E146" t="n">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="F146" t="n">
+      <c r="E146">
+        <v>8.87</v>
+      </c>
+      <c r="F146">
         <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147">
         <v>146</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147">
         <v>37.9</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147">
         <v>37</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147">
         <v>23</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E147">
         <v>14.88</v>
       </c>
-      <c r="F147" t="n">
+      <c r="F147">
         <v>1</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148">
         <v>31.9</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148">
         <v>42.4</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148">
         <v>15</v>
       </c>
-      <c r="E148" t="n">
+      <c r="E148">
         <v>13.62</v>
       </c>
-      <c r="F148" t="n">
+      <c r="F148">
         <v>1</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149">
         <v>22.9</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149">
         <v>57.6</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149">
         <v>19</v>
       </c>
-      <c r="E149" t="n">
+      <c r="E149">
         <v>8.23</v>
       </c>
-      <c r="F149" t="n">
+      <c r="F149">
         <v>0</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150">
         <v>22.4</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150">
         <v>39.8</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150">
         <v>27</v>
       </c>
-      <c r="E150" t="n">
+      <c r="E150">
         <v>13.35</v>
       </c>
-      <c r="F150" t="n">
+      <c r="F150">
         <v>1</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151">
         <v>150</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151">
         <v>27.5</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151">
         <v>25.3</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151">
         <v>10</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E151">
         <v>10.64</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F151">
         <v>1</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152">
         <v>151</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152">
         <v>24.7</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152">
         <v>45.4</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152">
         <v>20</v>
       </c>
-      <c r="E152" t="n">
+      <c r="E152">
         <v>9.76</v>
       </c>
-      <c r="F152" t="n">
+      <c r="F152">
         <v>0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153">
         <v>152</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153">
         <v>19.6</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153">
         <v>55.4</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153">
         <v>17</v>
       </c>
-      <c r="E153" t="n">
+      <c r="E153">
         <v>10.92</v>
       </c>
-      <c r="F153" t="n">
+      <c r="F153">
         <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154">
         <v>153</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154">
         <v>20.5</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154">
         <v>57.8</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154">
         <v>14</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E154">
         <v>10.13</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F154">
         <v>0</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155">
         <v>154</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155">
         <v>19.2</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155">
         <v>44.5</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155">
         <v>24</v>
       </c>
-      <c r="E155" t="n">
+      <c r="E155">
         <v>15.23</v>
       </c>
-      <c r="F155" t="n">
+      <c r="F155">
         <v>1</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156">
         <v>155</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156">
         <v>16.6</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156">
         <v>60</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156">
         <v>17</v>
       </c>
-      <c r="E156" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="F156" t="n">
+      <c r="E156">
+        <v>9.05</v>
+      </c>
+      <c r="F156">
         <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157">
         <v>156</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157">
         <v>18.6</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157">
         <v>34.7</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157">
         <v>12</v>
       </c>
-      <c r="E157" t="n">
+      <c r="E157">
         <v>13.9</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F157">
         <v>1</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158">
         <v>157</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158">
         <v>27.7</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158">
         <v>59</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158">
         <v>18</v>
       </c>
-      <c r="E158" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="F158" t="n">
+      <c r="E158">
+        <v>9.89</v>
+      </c>
+      <c r="F158">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159">
         <v>158</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159">
         <v>21.9</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159">
         <v>51.5</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159">
         <v>10</v>
       </c>
-      <c r="E159" t="n">
+      <c r="E159">
         <v>14.62</v>
       </c>
-      <c r="F159" t="n">
+      <c r="F159">
         <v>0</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160">
         <v>159</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160">
         <v>28.9</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160">
         <v>46.7</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160">
         <v>15</v>
       </c>
-      <c r="E160" t="n">
+      <c r="E160">
         <v>10.58</v>
       </c>
-      <c r="F160" t="n">
+      <c r="F160">
         <v>1</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161">
         <v>160</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161">
         <v>19.2</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161">
         <v>30</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161">
         <v>13</v>
       </c>
-      <c r="E161" t="n">
+      <c r="E161">
         <v>14.84</v>
       </c>
-      <c r="F161" t="n">
+      <c r="F161">
         <v>0</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162">
         <v>161</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162">
         <v>14.2</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162">
         <v>56.2</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162">
         <v>15</v>
       </c>
-      <c r="E162" t="n">
+      <c r="E162">
         <v>8.01</v>
       </c>
-      <c r="F162" t="n">
+      <c r="F162">
         <v>0</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163">
         <v>162</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163">
         <v>20.7</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163">
         <v>51.6</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163">
         <v>21</v>
       </c>
-      <c r="E163" t="n">
+      <c r="E163">
         <v>8.99</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F163">
         <v>0</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164">
         <v>163</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164">
         <v>23.5</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164">
         <v>55.4</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164">
         <v>13</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E164">
         <v>14.51</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F164">
         <v>1</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165">
         <v>164</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165">
         <v>16.1</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165">
         <v>51.3</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165">
         <v>6</v>
       </c>
-      <c r="E165" t="n">
+      <c r="E165">
         <v>11.26</v>
       </c>
-      <c r="F165" t="n">
+      <c r="F165">
         <v>0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166">
         <v>165</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166">
         <v>20.2</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166">
         <v>43.2</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166">
         <v>18</v>
       </c>
-      <c r="E166" t="n">
+      <c r="E166">
         <v>9.76</v>
       </c>
-      <c r="F166" t="n">
+      <c r="F166">
         <v>0</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167">
         <v>166</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167">
         <v>26.4</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167">
         <v>36.4</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167">
         <v>22</v>
       </c>
-      <c r="E167" t="n">
+      <c r="E167">
         <v>14.38</v>
       </c>
-      <c r="F167" t="n">
+      <c r="F167">
         <v>1</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168">
         <v>167</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168">
         <v>19.3</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168">
         <v>52.8</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168">
         <v>7</v>
       </c>
-      <c r="E168" t="n">
+      <c r="E168">
         <v>13.28</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F168">
         <v>0</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169">
         <v>168</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169">
         <v>22.9</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169">
         <v>44.2</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169">
         <v>19</v>
       </c>
-      <c r="E169" t="n">
+      <c r="E169">
         <v>20.28</v>
       </c>
-      <c r="F169" t="n">
+      <c r="F169">
         <v>1</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170">
         <v>169</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170">
         <v>22.1</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170">
         <v>37.6</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170">
         <v>17</v>
       </c>
-      <c r="E170" t="n">
+      <c r="E170">
         <v>14.85</v>
       </c>
-      <c r="F170" t="n">
+      <c r="F170">
         <v>1</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171">
         <v>170</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171">
         <v>20</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171">
         <v>42.5</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171">
         <v>19</v>
       </c>
-      <c r="E171" t="n">
+      <c r="E171">
         <v>11.56</v>
       </c>
-      <c r="F171" t="n">
+      <c r="F171">
         <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172">
         <v>171</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172">
         <v>30.9</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172">
         <v>52.6</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172">
         <v>9</v>
       </c>
-      <c r="E172" t="n">
+      <c r="E172">
         <v>13.59</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F172">
         <v>1</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173">
         <v>172</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173">
         <v>13.6</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173">
         <v>48.3</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173">
         <v>8</v>
       </c>
-      <c r="E173" t="n">
+      <c r="E173">
         <v>13.95</v>
       </c>
-      <c r="F173" t="n">
+      <c r="F173">
         <v>0</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174">
         <v>173</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174">
         <v>17.4</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174">
         <v>49.5</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174">
         <v>7</v>
       </c>
-      <c r="E174" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="F174" t="n">
+      <c r="E174">
+        <v>9.55</v>
+      </c>
+      <c r="F174">
         <v>0</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175">
         <v>19.4</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175">
         <v>46.3</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175">
         <v>24</v>
       </c>
-      <c r="E175" t="n">
+      <c r="E175">
         <v>11.1</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F175">
         <v>0</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176">
         <v>175</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176">
         <v>19.4</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176">
         <v>59.8</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176">
         <v>18</v>
       </c>
-      <c r="E176" t="n">
+      <c r="E176">
         <v>7.25</v>
       </c>
-      <c r="F176" t="n">
+      <c r="F176">
         <v>0</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177">
         <v>176</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177">
         <v>23.6</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177">
         <v>49.8</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177">
         <v>11</v>
       </c>
-      <c r="E177" t="n">
+      <c r="E177">
         <v>7.25</v>
       </c>
-      <c r="F177" t="n">
+      <c r="F177">
         <v>1</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178">
         <v>177</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178">
         <v>27.7</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178">
         <v>42.8</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178">
         <v>5</v>
       </c>
-      <c r="E178" t="n">
+      <c r="E178">
         <v>15.46</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F178">
         <v>0</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179">
         <v>178</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179">
         <v>27.6</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179">
         <v>41.5</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179">
         <v>24</v>
       </c>
-      <c r="E179" t="n">
+      <c r="E179">
         <v>16.48</v>
       </c>
-      <c r="F179" t="n">
+      <c r="F179">
         <v>1</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180">
         <v>179</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180">
         <v>16.1</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180">
         <v>43.5</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180">
         <v>14</v>
       </c>
-      <c r="E180" t="n">
+      <c r="E180">
         <v>12.11</v>
       </c>
-      <c r="F180" t="n">
+      <c r="F180">
         <v>0</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181">
         <v>180</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181">
         <v>18.5</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181">
         <v>55</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181">
         <v>8</v>
       </c>
-      <c r="E181" t="n">
+      <c r="E181">
         <v>11.53</v>
       </c>
-      <c r="F181" t="n">
+      <c r="F181">
         <v>1</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182">
         <v>181</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182">
         <v>19.3</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182">
         <v>53.1</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182">
         <v>18</v>
       </c>
-      <c r="E182" t="n">
+      <c r="E182">
         <v>5.81</v>
       </c>
-      <c r="F182" t="n">
+      <c r="F182">
         <v>0</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183">
         <v>182</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183">
         <v>25.9</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183">
         <v>48</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183">
         <v>19</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183">
         <v>9.25</v>
       </c>
-      <c r="F183" t="n">
+      <c r="F183">
         <v>0</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184">
         <v>183</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184">
         <v>20.8</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184">
         <v>47.6</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184">
         <v>13</v>
       </c>
-      <c r="E184" t="n">
+      <c r="E184">
         <v>10.13</v>
       </c>
-      <c r="F184" t="n">
+      <c r="F184">
         <v>0</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
+      <c r="A185">
         <v>184</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185">
         <v>10.7</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C185">
         <v>53.8</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185">
         <v>11</v>
       </c>
-      <c r="E185" t="n">
+      <c r="E185">
         <v>11.63</v>
       </c>
-      <c r="F185" t="n">
+      <c r="F185">
         <v>0</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186">
         <v>185</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186">
         <v>20.5</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186">
         <v>40.3</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186">
         <v>11</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E186">
         <v>13.87</v>
       </c>
-      <c r="F186" t="n">
+      <c r="F186">
         <v>1</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187">
         <v>186</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187">
         <v>20.5</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187">
         <v>60.8</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187">
         <v>12</v>
       </c>
-      <c r="E187" t="n">
+      <c r="E187">
         <v>13.01</v>
       </c>
-      <c r="F187" t="n">
+      <c r="F187">
         <v>0</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188">
         <v>187</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188">
         <v>24.3</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188">
         <v>43.5</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188">
         <v>20</v>
       </c>
-      <c r="E188" t="n">
+      <c r="E188">
         <v>10.7</v>
       </c>
-      <c r="F188" t="n">
+      <c r="F188">
         <v>0</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
+      <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189">
         <v>26.6</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189">
         <v>33.4</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189">
         <v>25</v>
       </c>
-      <c r="E189" t="n">
+      <c r="E189">
         <v>14.61</v>
       </c>
-      <c r="F189" t="n">
+      <c r="F189">
         <v>1</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
+      <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190">
         <v>20.6</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190">
         <v>59.9</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190">
         <v>9</v>
       </c>
-      <c r="E190" t="n">
+      <c r="E190">
         <v>12.72</v>
       </c>
-      <c r="F190" t="n">
+      <c r="F190">
         <v>0</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
+      <c r="A191">
         <v>190</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191">
         <v>24.3</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191">
         <v>47</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191">
         <v>12</v>
       </c>
-      <c r="E191" t="n">
+      <c r="E191">
         <v>8.19</v>
       </c>
-      <c r="F191" t="n">
+      <c r="F191">
         <v>0</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192">
         <v>191</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192">
         <v>31</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192">
         <v>51.9</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192">
         <v>17</v>
       </c>
-      <c r="E192" t="n">
+      <c r="E192">
         <v>14.8</v>
       </c>
-      <c r="F192" t="n">
+      <c r="F192">
         <v>1</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193">
         <v>192</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193">
         <v>17.3</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193">
         <v>56.2</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193">
         <v>15</v>
       </c>
-      <c r="E193" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="F193" t="n">
+      <c r="E193">
+        <v>8.47</v>
+      </c>
+      <c r="F193">
         <v>0</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194">
         <v>193</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194">
         <v>21.8</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194">
         <v>40.5</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194">
         <v>12</v>
       </c>
-      <c r="E194" t="n">
+      <c r="E194">
         <v>8.18</v>
       </c>
-      <c r="F194" t="n">
+      <c r="F194">
         <v>0</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
+      <c r="A195">
         <v>194</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195">
         <v>16.2</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195">
         <v>45.7</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195">
         <v>17</v>
       </c>
-      <c r="E195" t="n">
+      <c r="E195">
         <v>13.59</v>
       </c>
-      <c r="F195" t="n">
+      <c r="F195">
         <v>0</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
+      <c r="A196">
         <v>195</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196">
         <v>15.7</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196">
         <v>50.3</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196">
         <v>18</v>
       </c>
-      <c r="E196" t="n">
+      <c r="E196">
         <v>12.55</v>
       </c>
-      <c r="F196" t="n">
+      <c r="F196">
         <v>0</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
+      <c r="A197">
         <v>196</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197">
         <v>22.4</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197">
         <v>48.5</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197">
         <v>5</v>
       </c>
-      <c r="E197" t="n">
+      <c r="E197">
         <v>11.17</v>
       </c>
-      <c r="F197" t="n">
+      <c r="F197">
         <v>0</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198">
         <v>197</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198">
         <v>14.3</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198">
         <v>52.1</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198">
         <v>5</v>
       </c>
-      <c r="E198" t="n">
+      <c r="E198">
         <v>13.09</v>
       </c>
-      <c r="F198" t="n">
+      <c r="F198">
         <v>0</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
+      <c r="A199">
         <v>198</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199">
         <v>26.7</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199">
         <v>37.7</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199">
         <v>21</v>
       </c>
-      <c r="E199" t="n">
+      <c r="E199">
         <v>14.78</v>
       </c>
-      <c r="F199" t="n">
+      <c r="F199">
         <v>1</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
+      <c r="A200">
         <v>199</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200">
         <v>27.3</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200">
         <v>41.4</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200">
         <v>24</v>
       </c>
-      <c r="E200" t="n">
+      <c r="E200">
         <v>17.2</v>
       </c>
-      <c r="F200" t="n">
+      <c r="F200">
         <v>1</v>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201">
         <v>200</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201">
         <v>23.4</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201">
         <v>57</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201">
         <v>23</v>
       </c>
-      <c r="E201" t="n">
+      <c r="E201">
         <v>7.76</v>
       </c>
-      <c r="F201" t="n">
+      <c r="F201">
         <v>0</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202">
         <v>201</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202">
         <v>15.4</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202">
         <v>59.3</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202">
         <v>15</v>
       </c>
-      <c r="E202" t="n">
+      <c r="E202">
         <v>9.49</v>
       </c>
-      <c r="F202" t="n">
+      <c r="F202">
         <v>0</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203">
         <v>202</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203">
         <v>21.5</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203">
         <v>44.5</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203">
         <v>13</v>
       </c>
-      <c r="E203" t="n">
+      <c r="E203">
         <v>10.8</v>
       </c>
-      <c r="F203" t="n">
+      <c r="F203">
         <v>0</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204">
         <v>203</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204">
         <v>25.5</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204">
         <v>40.4</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204">
         <v>11</v>
       </c>
-      <c r="E204" t="n">
+      <c r="E204">
         <v>11.37</v>
       </c>
-      <c r="F204" t="n">
+      <c r="F204">
         <v>1</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205">
         <v>204</v>
       </c>
-      <c r="B205" t="n">
+      <c r="B205">
         <v>25.9</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205">
         <v>49.1</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205">
         <v>21</v>
       </c>
-      <c r="E205" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F205" t="n">
+      <c r="E205">
+        <v>8.2</v>
+      </c>
+      <c r="F205">
         <v>0</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206">
         <v>205</v>
       </c>
-      <c r="B206" t="n">
+      <c r="B206">
         <v>17</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206">
         <v>40.6</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206">
         <v>7</v>
       </c>
-      <c r="E206" t="n">
+      <c r="E206">
         <v>6.79</v>
       </c>
-      <c r="F206" t="n">
+      <c r="F206">
         <v>0</v>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207">
         <v>206</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207">
         <v>15.6</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207">
         <v>56.6</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207">
         <v>9</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E207">
         <v>11.54</v>
       </c>
-      <c r="F207" t="n">
+      <c r="F207">
         <v>0</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208">
         <v>207</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208">
         <v>28</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208">
         <v>46</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208">
         <v>17</v>
       </c>
-      <c r="E208" t="n">
+      <c r="E208">
         <v>12.72</v>
       </c>
-      <c r="F208" t="n">
+      <c r="F208">
         <v>1</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209">
         <v>208</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209">
         <v>22.6</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209">
         <v>45.6</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209">
         <v>18</v>
       </c>
-      <c r="E209" t="n">
+      <c r="E209">
         <v>14.53</v>
       </c>
-      <c r="F209" t="n">
+      <c r="F209">
         <v>1</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210">
         <v>209</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210">
         <v>14.8</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210">
         <v>49.2</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210">
         <v>16</v>
       </c>
-      <c r="E210" t="n">
+      <c r="E210">
         <v>11.16</v>
       </c>
-      <c r="F210" t="n">
+      <c r="F210">
         <v>0</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211">
         <v>210</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211">
         <v>23.6</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211">
         <v>56.1</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211">
         <v>9</v>
       </c>
-      <c r="E211" t="n">
+      <c r="E211">
         <v>9.48</v>
       </c>
-      <c r="F211" t="n">
+      <c r="F211">
         <v>0</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212">
         <v>211</v>
       </c>
-      <c r="B212" t="n">
+      <c r="B212">
         <v>27.7</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212">
         <v>48.7</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212">
         <v>12</v>
       </c>
-      <c r="E212" t="n">
+      <c r="E212">
         <v>13.92</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F212">
         <v>1</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213">
         <v>212</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213">
         <v>7.6</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213">
         <v>58.1</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213">
         <v>9</v>
       </c>
-      <c r="E213" t="n">
+      <c r="E213">
         <v>10.21</v>
       </c>
-      <c r="F213" t="n">
+      <c r="F213">
         <v>0</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214">
         <v>213</v>
       </c>
-      <c r="B214" t="n">
+      <c r="B214">
         <v>22.3</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C214">
         <v>40.8</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214">
         <v>14</v>
       </c>
-      <c r="E214" t="n">
+      <c r="E214">
         <v>14.92</v>
       </c>
-      <c r="F214" t="n">
+      <c r="F214">
         <v>1</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215">
         <v>214</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215">
         <v>15.6</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215">
         <v>52.4</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215">
         <v>17</v>
       </c>
-      <c r="E215" t="n">
+      <c r="E215">
         <v>13.18</v>
       </c>
-      <c r="F215" t="n">
+      <c r="F215">
         <v>0</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216">
         <v>215</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216">
         <v>28.6</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216">
         <v>39.3</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216">
         <v>12</v>
       </c>
-      <c r="E216" t="n">
+      <c r="E216">
         <v>11.16</v>
       </c>
-      <c r="F216" t="n">
+      <c r="F216">
         <v>1</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217">
         <v>216</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217">
         <v>31.9</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217">
         <v>39.7</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217">
         <v>8</v>
       </c>
-      <c r="E217" t="n">
+      <c r="E217">
         <v>14.09</v>
       </c>
-      <c r="F217" t="n">
+      <c r="F217">
         <v>1</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218">
         <v>217</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218">
         <v>34.2</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C218">
         <v>48.9</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218">
         <v>20</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E218">
         <v>10.91</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F218">
         <v>1</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219">
         <v>218</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219">
         <v>22.8</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219">
         <v>50.4</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219">
         <v>24</v>
       </c>
-      <c r="E219" t="n">
+      <c r="E219">
         <v>13.44</v>
       </c>
-      <c r="F219" t="n">
+      <c r="F219">
         <v>0</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220">
         <v>219</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220">
         <v>15.6</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220">
         <v>48.9</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220">
         <v>19</v>
       </c>
-      <c r="E220" t="n">
+      <c r="E220">
         <v>5.36</v>
       </c>
-      <c r="F220" t="n">
+      <c r="F220">
         <v>0</v>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221">
         <v>220</v>
       </c>
-      <c r="B221" t="n">
+      <c r="B221">
         <v>21.5</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221">
         <v>46.2</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221">
         <v>22</v>
       </c>
-      <c r="E221" t="n">
+      <c r="E221">
         <v>14.28</v>
       </c>
-      <c r="F221" t="n">
+      <c r="F221">
         <v>1</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222">
         <v>221</v>
       </c>
-      <c r="B222" t="n">
+      <c r="B222">
         <v>16.2</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C222">
         <v>54.7</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222">
         <v>12</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E222">
         <v>8.84</v>
       </c>
-      <c r="F222" t="n">
+      <c r="F222">
         <v>0</v>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223">
         <v>222</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223">
         <v>22</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C223">
         <v>44.7</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223">
         <v>10</v>
       </c>
-      <c r="E223" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="F223" t="n">
+      <c r="E223">
+        <v>8.45</v>
+      </c>
+      <c r="F223">
         <v>0</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224">
         <v>223</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224">
         <v>25.1</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C224">
         <v>45.5</v>
       </c>
-      <c r="D224" t="n">
+      <c r="D224">
         <v>18</v>
       </c>
-      <c r="E224" t="n">
+      <c r="E224">
         <v>11.63</v>
       </c>
-      <c r="F224" t="n">
+      <c r="F224">
         <v>0</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225">
         <v>224</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225">
         <v>12.3</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225">
         <v>55</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D225">
         <v>17</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E225">
         <v>11.18</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F225">
         <v>0</v>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226">
         <v>225</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226">
         <v>22.4</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226">
         <v>53.7</v>
       </c>
-      <c r="D226" t="n">
+      <c r="D226">
         <v>20</v>
       </c>
-      <c r="E226" t="n">
+      <c r="E226">
         <v>7.51</v>
       </c>
-      <c r="F226" t="n">
+      <c r="F226">
         <v>0</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227">
         <v>226</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227">
         <v>23.7</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227">
         <v>48.5</v>
       </c>
-      <c r="D227" t="n">
+      <c r="D227">
         <v>6</v>
       </c>
-      <c r="E227" t="n">
+      <c r="E227">
         <v>11.01</v>
       </c>
-      <c r="F227" t="n">
+      <c r="F227">
         <v>0</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228">
         <v>227</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228">
         <v>21.3</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228">
         <v>58.4</v>
       </c>
-      <c r="D228" t="n">
+      <c r="D228">
         <v>9</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E228">
         <v>10.58</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F228">
         <v>0</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229">
         <v>228</v>
       </c>
-      <c r="B229" t="n">
+      <c r="B229">
         <v>32.9</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229">
         <v>49.3</v>
       </c>
-      <c r="D229" t="n">
+      <c r="D229">
         <v>18</v>
       </c>
-      <c r="E229" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="F229" t="n">
+      <c r="E229">
+        <v>8.03</v>
+      </c>
+      <c r="F229">
         <v>0</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230">
         <v>229</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230">
         <v>22.1</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230">
         <v>36.5</v>
       </c>
-      <c r="D230" t="n">
+      <c r="D230">
         <v>23</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E230">
         <v>6.28</v>
       </c>
-      <c r="F230" t="n">
+      <c r="F230">
         <v>0</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231">
         <v>230</v>
       </c>
-      <c r="B231" t="n">
+      <c r="B231">
         <v>20.1</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C231">
         <v>44.4</v>
       </c>
-      <c r="D231" t="n">
+      <c r="D231">
         <v>21</v>
       </c>
-      <c r="E231" t="n">
+      <c r="E231">
         <v>11.81</v>
       </c>
-      <c r="F231" t="n">
+      <c r="F231">
         <v>0</v>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232">
         <v>231</v>
       </c>
-      <c r="B232" t="n">
+      <c r="B232">
         <v>28.4</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C232">
         <v>31.7</v>
       </c>
-      <c r="D232" t="n">
+      <c r="D232">
         <v>22</v>
       </c>
-      <c r="E232" t="n">
+      <c r="E232">
         <v>15.58</v>
       </c>
-      <c r="F232" t="n">
+      <c r="F232">
         <v>1</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233">
         <v>232</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233">
         <v>23.8</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C233">
         <v>50</v>
       </c>
-      <c r="D233" t="n">
+      <c r="D233">
         <v>24</v>
       </c>
-      <c r="E233" t="n">
+      <c r="E233">
         <v>15.14</v>
       </c>
-      <c r="F233" t="n">
+      <c r="F233">
         <v>1</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234">
         <v>233</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234">
         <v>15.6</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C234">
         <v>53.5</v>
       </c>
-      <c r="D234" t="n">
+      <c r="D234">
         <v>23</v>
       </c>
-      <c r="E234" t="n">
+      <c r="E234">
         <v>8.56</v>
       </c>
-      <c r="F234" t="n">
+      <c r="F234">
         <v>0</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235">
         <v>234</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235">
         <v>21.7</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C235">
         <v>50.8</v>
       </c>
-      <c r="D235" t="n">
+      <c r="D235">
         <v>7</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E235">
         <v>12.84</v>
       </c>
-      <c r="F235" t="n">
+      <c r="F235">
         <v>0</v>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236">
         <v>235</v>
       </c>
-      <c r="B236" t="n">
+      <c r="B236">
         <v>24.6</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C236">
         <v>33.8</v>
       </c>
-      <c r="D236" t="n">
+      <c r="D236">
         <v>20</v>
       </c>
-      <c r="E236" t="n">
+      <c r="E236">
         <v>18.33</v>
       </c>
-      <c r="F236" t="n">
+      <c r="F236">
         <v>0</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237">
         <v>236</v>
       </c>
-      <c r="B237" t="n">
+      <c r="B237">
         <v>19.1</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C237">
         <v>39.7</v>
       </c>
-      <c r="D237" t="n">
+      <c r="D237">
         <v>7</v>
       </c>
-      <c r="E237" t="n">
+      <c r="E237">
         <v>10.25</v>
       </c>
-      <c r="F237" t="n">
+      <c r="F237">
         <v>0</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238">
         <v>237</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238">
         <v>29.7</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C238">
         <v>40.9</v>
       </c>
-      <c r="D238" t="n">
+      <c r="D238">
         <v>16</v>
       </c>
-      <c r="E238" t="n">
+      <c r="E238">
         <v>15.16</v>
       </c>
-      <c r="F238" t="n">
+      <c r="F238">
         <v>1</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239">
         <v>238</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239">
         <v>18.5</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C239">
         <v>37.5</v>
       </c>
-      <c r="D239" t="n">
+      <c r="D239">
         <v>18</v>
       </c>
-      <c r="E239" t="n">
+      <c r="E239">
         <v>7.84</v>
       </c>
-      <c r="F239" t="n">
+      <c r="F239">
         <v>0</v>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240">
         <v>239</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240">
         <v>26.5</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C240">
         <v>56.6</v>
       </c>
-      <c r="D240" t="n">
+      <c r="D240">
         <v>11</v>
       </c>
-      <c r="E240" t="n">
+      <c r="E240">
         <v>7.86</v>
       </c>
-      <c r="F240" t="n">
+      <c r="F240">
         <v>0</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241">
         <v>240</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241">
         <v>20.9</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C241">
         <v>49.3</v>
       </c>
-      <c r="D241" t="n">
+      <c r="D241">
         <v>10</v>
       </c>
-      <c r="E241" t="n">
+      <c r="E241">
         <v>14.18</v>
       </c>
-      <c r="F241" t="n">
+      <c r="F241">
         <v>0</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242">
         <v>241</v>
       </c>
-      <c r="B242" t="n">
+      <c r="B242">
         <v>22.1</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C242">
         <v>49</v>
       </c>
-      <c r="D242" t="n">
+      <c r="D242">
         <v>9</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E242">
         <v>15.45</v>
       </c>
-      <c r="F242" t="n">
+      <c r="F242">
         <v>0</v>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243">
         <v>242</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243">
         <v>23.1</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C243">
         <v>49.6</v>
       </c>
-      <c r="D243" t="n">
+      <c r="D243">
         <v>23</v>
       </c>
-      <c r="E243" t="n">
+      <c r="E243">
         <v>9.23</v>
       </c>
-      <c r="F243" t="n">
+      <c r="F243">
         <v>0</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244">
         <v>243</v>
       </c>
-      <c r="B244" t="n">
+      <c r="B244">
         <v>14.6</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C244">
         <v>43.3</v>
       </c>
-      <c r="D244" t="n">
+      <c r="D244">
         <v>5</v>
       </c>
-      <c r="E244" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="F244" t="n">
+      <c r="E244">
+        <v>8.22</v>
+      </c>
+      <c r="F244">
         <v>0</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245">
         <v>244</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245">
         <v>19.3</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C245">
         <v>42.7</v>
       </c>
-      <c r="D245" t="n">
+      <c r="D245">
         <v>16</v>
       </c>
-      <c r="E245" t="n">
+      <c r="E245">
         <v>7.56</v>
       </c>
-      <c r="F245" t="n">
+      <c r="F245">
         <v>0</v>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246">
         <v>245</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246">
         <v>33.4</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C246">
         <v>28.7</v>
       </c>
-      <c r="D246" t="n">
+      <c r="D246">
         <v>10</v>
       </c>
-      <c r="E246" t="n">
+      <c r="E246">
         <v>12.32</v>
       </c>
-      <c r="F246" t="n">
+      <c r="F246">
         <v>1</v>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247">
         <v>246</v>
       </c>
-      <c r="B247" t="n">
+      <c r="B247">
         <v>26.1</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C247">
         <v>42.2</v>
       </c>
-      <c r="D247" t="n">
+      <c r="D247">
         <v>19</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E247">
         <v>13.96</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F247">
         <v>1</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248">
         <v>247</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248">
         <v>25.6</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C248">
         <v>52.8</v>
       </c>
-      <c r="D248" t="n">
+      <c r="D248">
         <v>19</v>
       </c>
-      <c r="E248" t="n">
+      <c r="E248">
         <v>6.74</v>
       </c>
-      <c r="F248" t="n">
+      <c r="F248">
         <v>0</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249">
         <v>248</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249">
         <v>29.5</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C249">
         <v>40.3</v>
       </c>
-      <c r="D249" t="n">
+      <c r="D249">
         <v>23</v>
       </c>
-      <c r="E249" t="n">
+      <c r="E249">
         <v>12.07</v>
       </c>
-      <c r="F249" t="n">
+      <c r="F249">
         <v>1</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250">
         <v>249</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250">
         <v>18.7</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C250">
         <v>40</v>
       </c>
-      <c r="D250" t="n">
+      <c r="D250">
         <v>11</v>
       </c>
-      <c r="E250" t="n">
+      <c r="E250">
         <v>16.16</v>
       </c>
-      <c r="F250" t="n">
+      <c r="F250">
         <v>1</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251">
         <v>250</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251">
         <v>28.8</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C251">
         <v>35.4</v>
       </c>
-      <c r="D251" t="n">
+      <c r="D251">
         <v>25</v>
       </c>
-      <c r="E251" t="n">
+      <c r="E251">
         <v>13.4</v>
       </c>
-      <c r="F251" t="n">
+      <c r="F251">
         <v>1</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252">
         <v>251</v>
       </c>
-      <c r="B252" t="n">
+      <c r="B252">
         <v>15.6</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C252">
         <v>51.8</v>
       </c>
-      <c r="D252" t="n">
+      <c r="D252">
         <v>11</v>
       </c>
-      <c r="E252" t="n">
+      <c r="E252">
         <v>7.87</v>
       </c>
-      <c r="F252" t="n">
+      <c r="F252">
         <v>0</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253">
         <v>252</v>
       </c>
-      <c r="B253" t="n">
+      <c r="B253">
         <v>27</v>
       </c>
-      <c r="C253" t="n">
+      <c r="C253">
         <v>24.8</v>
       </c>
-      <c r="D253" t="n">
+      <c r="D253">
         <v>17</v>
       </c>
-      <c r="E253" t="n">
+      <c r="E253">
         <v>10.89</v>
       </c>
-      <c r="F253" t="n">
+      <c r="F253">
         <v>1</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254">
         <v>253</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254">
         <v>24.3</v>
       </c>
-      <c r="C254" t="n">
+      <c r="C254">
         <v>34.3</v>
       </c>
-      <c r="D254" t="n">
+      <c r="D254">
         <v>26</v>
       </c>
-      <c r="E254" t="n">
+      <c r="E254">
         <v>16.45</v>
       </c>
-      <c r="F254" t="n">
+      <c r="F254">
         <v>1</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255">
         <v>254</v>
       </c>
-      <c r="B255" t="n">
+      <c r="B255">
         <v>20.1</v>
       </c>
-      <c r="C255" t="n">
+      <c r="C255">
         <v>45.4</v>
       </c>
-      <c r="D255" t="n">
+      <c r="D255">
         <v>16</v>
       </c>
-      <c r="E255" t="n">
+      <c r="E255">
         <v>7.2</v>
       </c>
-      <c r="F255" t="n">
+      <c r="F255">
         <v>0</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256">
         <v>255</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256">
         <v>19.7</v>
       </c>
-      <c r="C256" t="n">
+      <c r="C256">
         <v>46.4</v>
       </c>
-      <c r="D256" t="n">
+      <c r="D256">
         <v>21</v>
       </c>
-      <c r="E256" t="n">
+      <c r="E256">
         <v>9.44</v>
       </c>
-      <c r="F256" t="n">
+      <c r="F256">
         <v>0</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257">
         <v>256</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257">
         <v>21</v>
       </c>
-      <c r="C257" t="n">
+      <c r="C257">
         <v>51.5</v>
       </c>
-      <c r="D257" t="n">
+      <c r="D257">
         <v>6</v>
       </c>
-      <c r="E257" t="n">
+      <c r="E257">
         <v>12.27</v>
       </c>
-      <c r="F257" t="n">
+      <c r="F257">
         <v>0</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
+      <c r="A258">
         <v>257</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258">
         <v>18.2</v>
       </c>
-      <c r="C258" t="n">
+      <c r="C258">
         <v>48.7</v>
       </c>
-      <c r="D258" t="n">
+      <c r="D258">
         <v>21</v>
       </c>
-      <c r="E258" t="n">
+      <c r="E258">
         <v>11.13</v>
       </c>
-      <c r="F258" t="n">
+      <c r="F258">
         <v>0</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
+      <c r="A259">
         <v>258</v>
       </c>
-      <c r="B259" t="n">
+      <c r="B259">
         <v>14.6</v>
       </c>
-      <c r="C259" t="n">
+      <c r="C259">
         <v>51.1</v>
       </c>
-      <c r="D259" t="n">
+      <c r="D259">
         <v>23</v>
       </c>
-      <c r="E259" t="n">
+      <c r="E259">
         <v>10.51</v>
       </c>
-      <c r="F259" t="n">
+      <c r="F259">
         <v>0</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
+      <c r="A260">
         <v>259</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260">
         <v>16</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C260">
         <v>58.7</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D260">
         <v>7</v>
       </c>
-      <c r="E260" t="n">
+      <c r="E260">
         <v>10.54</v>
       </c>
-      <c r="F260" t="n">
+      <c r="F260">
         <v>0</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
+      <c r="A261">
         <v>260</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261">
         <v>23.7</v>
       </c>
-      <c r="C261" t="n">
+      <c r="C261">
         <v>59.6</v>
       </c>
-      <c r="D261" t="n">
+      <c r="D261">
         <v>22</v>
       </c>
-      <c r="E261" t="n">
+      <c r="E261">
         <v>7.44</v>
       </c>
-      <c r="F261" t="n">
+      <c r="F261">
         <v>0</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
+      <c r="A262">
         <v>261</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262">
         <v>26.9</v>
       </c>
-      <c r="C262" t="n">
+      <c r="C262">
         <v>54.5</v>
       </c>
-      <c r="D262" t="n">
+      <c r="D262">
         <v>16</v>
       </c>
-      <c r="E262" t="n">
+      <c r="E262">
         <v>8</v>
       </c>
-      <c r="F262" t="n">
+      <c r="F262">
         <v>0</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263">
         <v>262</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263">
         <v>20.9</v>
       </c>
-      <c r="C263" t="n">
+      <c r="C263">
         <v>58.7</v>
       </c>
-      <c r="D263" t="n">
+      <c r="D263">
         <v>6</v>
       </c>
-      <c r="E263" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="F263" t="n">
+      <c r="E263">
+        <v>8.64</v>
+      </c>
+      <c r="F263">
         <v>0</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
+      <c r="A264">
         <v>263</v>
       </c>
-      <c r="B264" t="n">
+      <c r="B264">
         <v>23.4</v>
       </c>
-      <c r="C264" t="n">
+      <c r="C264">
         <v>62.1</v>
       </c>
-      <c r="D264" t="n">
+      <c r="D264">
         <v>19</v>
       </c>
-      <c r="E264" t="n">
+      <c r="E264">
         <v>2.66</v>
       </c>
-      <c r="F264" t="n">
+      <c r="F264">
         <v>0</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
+      <c r="A265">
         <v>264</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265">
         <v>23.9</v>
       </c>
-      <c r="C265" t="n">
+      <c r="C265">
         <v>52.6</v>
       </c>
-      <c r="D265" t="n">
+      <c r="D265">
         <v>12</v>
       </c>
-      <c r="E265" t="n">
+      <c r="E265">
         <v>8.76</v>
       </c>
-      <c r="F265" t="n">
+      <c r="F265">
         <v>0</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
+      <c r="A266">
         <v>265</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266">
         <v>14.5</v>
       </c>
-      <c r="C266" t="n">
+      <c r="C266">
         <v>40.2</v>
       </c>
-      <c r="D266" t="n">
+      <c r="D266">
         <v>9</v>
       </c>
-      <c r="E266" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="F266" t="n">
+      <c r="E266">
+        <v>9.54</v>
+      </c>
+      <c r="F266">
         <v>0</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267">
         <v>266</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267">
         <v>18.5</v>
       </c>
-      <c r="C267" t="n">
+      <c r="C267">
         <v>49</v>
       </c>
-      <c r="D267" t="n">
+      <c r="D267">
         <v>25</v>
       </c>
-      <c r="E267" t="n">
+      <c r="E267">
         <v>13.59</v>
       </c>
-      <c r="F267" t="n">
+      <c r="F267">
         <v>1</v>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="n">
+      <c r="A268">
         <v>267</v>
       </c>
-      <c r="B268" t="n">
+      <c r="B268">
         <v>19.8</v>
       </c>
-      <c r="C268" t="n">
+      <c r="C268">
         <v>43</v>
       </c>
-      <c r="D268" t="n">
+      <c r="D268">
         <v>10</v>
       </c>
-      <c r="E268" t="n">
+      <c r="E268">
         <v>9.49</v>
       </c>
-      <c r="F268" t="n">
+      <c r="F268">
         <v>0</v>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
+      <c r="A269">
         <v>268</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269">
         <v>18.4</v>
       </c>
-      <c r="C269" t="n">
+      <c r="C269">
         <v>55</v>
       </c>
-      <c r="D269" t="n">
+      <c r="D269">
         <v>19</v>
       </c>
-      <c r="E269" t="n">
+      <c r="E269">
         <v>14.3</v>
       </c>
-      <c r="F269" t="n">
+      <c r="F269">
         <v>1</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
+      <c r="A270">
         <v>269</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270">
         <v>18.9</v>
       </c>
-      <c r="C270" t="n">
+      <c r="C270">
         <v>62.1</v>
       </c>
-      <c r="D270" t="n">
+      <c r="D270">
         <v>11</v>
       </c>
-      <c r="E270" t="n">
+      <c r="E270">
         <v>10.46</v>
       </c>
-      <c r="F270" t="n">
+      <c r="F270">
         <v>0</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271">
         <v>270</v>
       </c>
-      <c r="B271" t="n">
+      <c r="B271">
         <v>14.1</v>
       </c>
-      <c r="C271" t="n">
+      <c r="C271">
         <v>46.4</v>
       </c>
-      <c r="D271" t="n">
+      <c r="D271">
         <v>11</v>
       </c>
-      <c r="E271" t="n">
+      <c r="E271">
         <v>13.85</v>
       </c>
-      <c r="F271" t="n">
+      <c r="F271">
         <v>0</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272">
         <v>271</v>
       </c>
-      <c r="B272" t="n">
+      <c r="B272">
         <v>23.5</v>
       </c>
-      <c r="C272" t="n">
+      <c r="C272">
         <v>34.3</v>
       </c>
-      <c r="D272" t="n">
+      <c r="D272">
         <v>19</v>
       </c>
-      <c r="E272" t="n">
+      <c r="E272">
         <v>14.18</v>
       </c>
-      <c r="F272" t="n">
+      <c r="F272">
         <v>1</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273">
         <v>272</v>
       </c>
-      <c r="B273" t="n">
+      <c r="B273">
         <v>17</v>
       </c>
-      <c r="C273" t="n">
+      <c r="C273">
         <v>45.2</v>
       </c>
-      <c r="D273" t="n">
+      <c r="D273">
         <v>12</v>
       </c>
-      <c r="E273" t="n">
+      <c r="E273">
         <v>11.92</v>
       </c>
-      <c r="F273" t="n">
+      <c r="F273">
         <v>0</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274">
         <v>273</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274">
         <v>22.1</v>
       </c>
-      <c r="C274" t="n">
+      <c r="C274">
         <v>49.5</v>
       </c>
-      <c r="D274" t="n">
+      <c r="D274">
         <v>15</v>
       </c>
-      <c r="E274" t="n">
+      <c r="E274">
         <v>8.32</v>
       </c>
-      <c r="F274" t="n">
+      <c r="F274">
         <v>0</v>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
+      <c r="A275">
         <v>274</v>
       </c>
-      <c r="B275" t="n">
+      <c r="B275">
         <v>17.4</v>
       </c>
-      <c r="C275" t="n">
+      <c r="C275">
         <v>59</v>
       </c>
-      <c r="D275" t="n">
+      <c r="D275">
         <v>18</v>
       </c>
-      <c r="E275" t="n">
+      <c r="E275">
         <v>10.61</v>
       </c>
-      <c r="F275" t="n">
+      <c r="F275">
         <v>0</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276">
         <v>275</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276">
         <v>15.4</v>
       </c>
-      <c r="C276" t="n">
+      <c r="C276">
         <v>41.4</v>
       </c>
-      <c r="D276" t="n">
+      <c r="D276">
         <v>15</v>
       </c>
-      <c r="E276" t="n">
+      <c r="E276">
         <v>10.53</v>
       </c>
-      <c r="F276" t="n">
+      <c r="F276">
         <v>0</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
+      <c r="A277">
         <v>276</v>
       </c>
-      <c r="B277" t="n">
+      <c r="B277">
         <v>20.2</v>
       </c>
-      <c r="C277" t="n">
+      <c r="C277">
         <v>56.2</v>
       </c>
-      <c r="D277" t="n">
+      <c r="D277">
         <v>18</v>
       </c>
-      <c r="E277" t="n">
+      <c r="E277">
         <v>9.24</v>
       </c>
-      <c r="F277" t="n">
+      <c r="F277">
         <v>0</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
+      <c r="A278">
         <v>277</v>
       </c>
-      <c r="B278" t="n">
+      <c r="B278">
         <v>37.9</v>
       </c>
-      <c r="C278" t="n">
+      <c r="C278">
         <v>27.5</v>
       </c>
-      <c r="D278" t="n">
+      <c r="D278">
         <v>24</v>
       </c>
-      <c r="E278" t="n">
+      <c r="E278">
         <v>9.56</v>
       </c>
-      <c r="F278" t="n">
+      <c r="F278">
         <v>1</v>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279">
         <v>278</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279">
         <v>28</v>
       </c>
-      <c r="C279" t="n">
+      <c r="C279">
         <v>50.5</v>
       </c>
-      <c r="D279" t="n">
+      <c r="D279">
         <v>10</v>
       </c>
-      <c r="E279" t="n">
+      <c r="E279">
         <v>10.47</v>
       </c>
-      <c r="F279" t="n">
+      <c r="F279">
         <v>1</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280">
         <v>279</v>
       </c>
-      <c r="B280" t="n">
+      <c r="B280">
         <v>12.2</v>
       </c>
-      <c r="C280" t="n">
+      <c r="C280">
         <v>49.6</v>
       </c>
-      <c r="D280" t="n">
+      <c r="D280">
         <v>7</v>
       </c>
-      <c r="E280" t="n">
+      <c r="E280">
         <v>10.93</v>
       </c>
-      <c r="F280" t="n">
+      <c r="F280">
         <v>0</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281">
         <v>280</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281">
         <v>20.4</v>
       </c>
-      <c r="C281" t="n">
+      <c r="C281">
         <v>51.4</v>
       </c>
-      <c r="D281" t="n">
+      <c r="D281">
         <v>13</v>
       </c>
-      <c r="E281" t="n">
+      <c r="E281">
         <v>9.69</v>
       </c>
-      <c r="F281" t="n">
+      <c r="F281">
         <v>0</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282">
         <v>281</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282">
         <v>30.3</v>
       </c>
-      <c r="C282" t="n">
+      <c r="C282">
         <v>49.3</v>
       </c>
-      <c r="D282" t="n">
+      <c r="D282">
         <v>19</v>
       </c>
-      <c r="E282" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="F282" t="n">
+      <c r="E282">
+        <v>9.21</v>
+      </c>
+      <c r="F282">
         <v>0</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283">
         <v>282</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283">
         <v>26.7</v>
       </c>
-      <c r="C283" t="n">
+      <c r="C283">
         <v>48.6</v>
       </c>
-      <c r="D283" t="n">
+      <c r="D283">
         <v>24</v>
       </c>
-      <c r="E283" t="n">
+      <c r="E283">
         <v>12.14</v>
       </c>
-      <c r="F283" t="n">
+      <c r="F283">
         <v>1</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284">
         <v>283</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284">
         <v>31.1</v>
       </c>
-      <c r="C284" t="n">
+      <c r="C284">
         <v>44.6</v>
       </c>
-      <c r="D284" t="n">
+      <c r="D284">
         <v>17</v>
       </c>
-      <c r="E284" t="n">
+      <c r="E284">
         <v>14.05</v>
       </c>
-      <c r="F284" t="n">
+      <c r="F284">
         <v>1</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285">
         <v>284</v>
       </c>
-      <c r="B285" t="n">
+      <c r="B285">
         <v>24.4</v>
       </c>
-      <c r="C285" t="n">
+      <c r="C285">
         <v>61.8</v>
       </c>
-      <c r="D285" t="n">
+      <c r="D285">
         <v>21</v>
       </c>
-      <c r="E285" t="n">
+      <c r="E285">
         <v>11.25</v>
       </c>
-      <c r="F285" t="n">
+      <c r="F285">
         <v>0</v>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286">
         <v>285</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286">
         <v>24.8</v>
       </c>
-      <c r="C286" t="n">
+      <c r="C286">
         <v>37.6</v>
       </c>
-      <c r="D286" t="n">
+      <c r="D286">
         <v>8</v>
       </c>
-      <c r="E286" t="n">
+      <c r="E286">
         <v>14.46</v>
       </c>
-      <c r="F286" t="n">
+      <c r="F286">
         <v>0</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287">
         <v>286</v>
       </c>
-      <c r="B287" t="n">
+      <c r="B287">
         <v>24.2</v>
       </c>
-      <c r="C287" t="n">
+      <c r="C287">
         <v>43.7</v>
       </c>
-      <c r="D287" t="n">
+      <c r="D287">
         <v>18</v>
       </c>
-      <c r="E287" t="n">
+      <c r="E287">
         <v>9.81</v>
       </c>
-      <c r="F287" t="n">
+      <c r="F287">
         <v>0</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288">
         <v>287</v>
       </c>
-      <c r="B288" t="n">
+      <c r="B288">
         <v>21.1</v>
       </c>
-      <c r="C288" t="n">
+      <c r="C288">
         <v>40.6</v>
       </c>
-      <c r="D288" t="n">
+      <c r="D288">
         <v>18</v>
       </c>
-      <c r="E288" t="n">
+      <c r="E288">
         <v>9.41</v>
       </c>
-      <c r="F288" t="n">
+      <c r="F288">
         <v>0</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
+      <c r="A289">
         <v>288</v>
       </c>
-      <c r="B289" t="n">
+      <c r="B289">
         <v>19.3</v>
       </c>
-      <c r="C289" t="n">
+      <c r="C289">
         <v>55</v>
       </c>
-      <c r="D289" t="n">
+      <c r="D289">
         <v>21</v>
       </c>
-      <c r="E289" t="n">
+      <c r="E289">
         <v>10.53</v>
       </c>
-      <c r="F289" t="n">
+      <c r="F289">
         <v>0</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
+      <c r="A290">
         <v>289</v>
       </c>
-      <c r="B290" t="n">
+      <c r="B290">
         <v>18.9</v>
       </c>
-      <c r="C290" t="n">
+      <c r="C290">
         <v>38.2</v>
       </c>
-      <c r="D290" t="n">
+      <c r="D290">
         <v>5</v>
       </c>
-      <c r="E290" t="n">
+      <c r="E290">
         <v>12.76</v>
       </c>
-      <c r="F290" t="n">
+      <c r="F290">
         <v>0</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="n">
+      <c r="A291">
         <v>290</v>
       </c>
-      <c r="B291" t="n">
+      <c r="B291">
         <v>20.5</v>
       </c>
-      <c r="C291" t="n">
+      <c r="C291">
         <v>67</v>
       </c>
-      <c r="D291" t="n">
+      <c r="D291">
         <v>18</v>
       </c>
-      <c r="E291" t="n">
+      <c r="E291">
         <v>15.61</v>
       </c>
-      <c r="F291" t="n">
+      <c r="F291">
         <v>0</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
+      <c r="A292">
         <v>291</v>
       </c>
-      <c r="B292" t="n">
+      <c r="B292">
         <v>21.7</v>
       </c>
-      <c r="C292" t="n">
+      <c r="C292">
         <v>50.6</v>
       </c>
-      <c r="D292" t="n">
+      <c r="D292">
         <v>15</v>
       </c>
-      <c r="E292" t="n">
+      <c r="E292">
         <v>11.26</v>
       </c>
-      <c r="F292" t="n">
+      <c r="F292">
         <v>0</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
+      <c r="A293">
         <v>292</v>
       </c>
-      <c r="B293" t="n">
+      <c r="B293">
         <v>14.9</v>
       </c>
-      <c r="C293" t="n">
+      <c r="C293">
         <v>58.6</v>
       </c>
-      <c r="D293" t="n">
+      <c r="D293">
         <v>21</v>
       </c>
-      <c r="E293" t="n">
+      <c r="E293">
         <v>6.29</v>
       </c>
-      <c r="F293" t="n">
+      <c r="F293">
         <v>0</v>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
+      <c r="A294">
         <v>293</v>
       </c>
-      <c r="B294" t="n">
+      <c r="B294">
         <v>18.9</v>
       </c>
-      <c r="C294" t="n">
+      <c r="C294">
         <v>43.2</v>
       </c>
-      <c r="D294" t="n">
+      <c r="D294">
         <v>21</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294">
         <v>9.94</v>
       </c>
-      <c r="F294" t="n">
+      <c r="F294">
         <v>0</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
+      <c r="A295">
         <v>294</v>
       </c>
-      <c r="B295" t="n">
+      <c r="B295">
         <v>19.8</v>
       </c>
-      <c r="C295" t="n">
+      <c r="C295">
         <v>51.4</v>
       </c>
-      <c r="D295" t="n">
+      <c r="D295">
         <v>12</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295">
         <v>7.05</v>
       </c>
-      <c r="F295" t="n">
+      <c r="F295">
         <v>0</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296">
         <v>20.4</v>
       </c>
-      <c r="C296" t="n">
+      <c r="C296">
         <v>54.4</v>
       </c>
-      <c r="D296" t="n">
+      <c r="D296">
         <v>16</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296">
         <v>7.48</v>
       </c>
-      <c r="F296" t="n">
+      <c r="F296">
         <v>0</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
+      <c r="A297">
         <v>296</v>
       </c>
-      <c r="B297" t="n">
+      <c r="B297">
         <v>18.8</v>
       </c>
-      <c r="C297" t="n">
+      <c r="C297">
         <v>45.1</v>
       </c>
-      <c r="D297" t="n">
+      <c r="D297">
         <v>6</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E297">
         <v>14.39</v>
       </c>
-      <c r="F297" t="n">
+      <c r="F297">
         <v>0</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
+      <c r="A298">
         <v>297</v>
       </c>
-      <c r="B298" t="n">
+      <c r="B298">
         <v>29.2</v>
       </c>
-      <c r="C298" t="n">
+      <c r="C298">
         <v>40.4</v>
       </c>
-      <c r="D298" t="n">
+      <c r="D298">
         <v>10</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E298">
         <v>13.02</v>
       </c>
-      <c r="F298" t="n">
+      <c r="F298">
         <v>1</v>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
+      <c r="A299">
         <v>298</v>
       </c>
-      <c r="B299" t="n">
+      <c r="B299">
         <v>25.6</v>
       </c>
-      <c r="C299" t="n">
+      <c r="C299">
         <v>52.9</v>
       </c>
-      <c r="D299" t="n">
+      <c r="D299">
         <v>9</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E299">
         <v>12.11</v>
       </c>
-      <c r="F299" t="n">
+      <c r="F299">
         <v>1</v>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
+      <c r="A300">
         <v>299</v>
       </c>
-      <c r="B300" t="n">
+      <c r="B300">
         <v>18.5</v>
       </c>
-      <c r="C300" t="n">
+      <c r="C300">
         <v>58.9</v>
       </c>
-      <c r="D300" t="n">
+      <c r="D300">
         <v>17</v>
       </c>
-      <c r="E300" t="n">
+      <c r="E300">
         <v>13.31</v>
       </c>
-      <c r="F300" t="n">
+      <c r="F300">
         <v>0</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
+      <c r="A301">
         <v>300</v>
       </c>
-      <c r="B301" t="n">
+      <c r="B301">
         <v>15.1</v>
       </c>
-      <c r="C301" t="n">
+      <c r="C301">
         <v>54.1</v>
       </c>
-      <c r="D301" t="n">
+      <c r="D301">
         <v>16</v>
       </c>
-      <c r="E301" t="n">
+      <c r="E301">
         <v>10.09</v>
       </c>
-      <c r="F301" t="n">
+      <c r="F301">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F301"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>BD1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>BD2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>BD3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>BD4</t>
-        </is>
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>BD1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>BD2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>BD3</v>
+      </c>
+      <c r="E1" t="str">
+        <v>BD4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2">
         <v>301</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>31.5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>46.7</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>14</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>18.32</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3">
         <v>302</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>23.4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>55.8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>8.07</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4">
         <v>303</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>19.6</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>32.1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>17</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>10.86</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5">
         <v>304</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>16.3</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>55.6</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>14</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>7.69</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6">
         <v>305</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>29.6</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>46</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>23</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>7.97</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7">
         <v>306</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>16.1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>45.8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>12.21</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8">
         <v>307</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>31.6</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>38.8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>20</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>13.04</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9">
         <v>308</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>27.1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48.9</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>15</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>15.76</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10">
         <v>309</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>16.3</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>58.2</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>15</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>11.82</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11">
         <v>310</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>16.6</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>51.7</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>12</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>8.56</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12">
         <v>311</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>18.2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>54.8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>10.57</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13">
         <v>312</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>17.4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>64.2</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>11.77</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14">
         <v>313</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>14.2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>49.1</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>12.94</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15">
         <v>314</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>21.6</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>42.1</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>9</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>9.18</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16">
         <v>315</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>22.2</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>44.9</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>22</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>13.87</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17">
         <v>316</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>22.9</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>54.2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>16</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>7.51</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18">
         <v>317</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>19.2</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>48.1</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>16</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>11.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19">
         <v>318</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>20.5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>47.9</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>14</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>10.11</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20">
         <v>319</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>26.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>56.3</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>15</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>10.53</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21">
         <v>320</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>18.3</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>47.5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>21</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>8.99</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22">
         <v>321</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>25.5</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>35</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>19</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>13.57</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23">
         <v>322</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>26.6</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>22.5</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>24</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>12.4</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24">
         <v>323</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>29.1</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>55</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>14</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>8.07</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25">
         <v>324</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>14.7</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>58.2</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>6</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>5.79</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26">
         <v>325</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>23.1</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>33.1</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>19</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>14.11</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27">
         <v>326</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>18.3</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>53.4</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>20</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>8.81</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28">
         <v>327</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>14.8</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>46.9</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>18</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>12.16</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29">
         <v>328</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>14.5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>49.8</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>7</v>
       </c>
-      <c r="E29" t="n">
-        <v>9.619999999999999</v>
+      <c r="E29">
+        <v>9.62</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30">
         <v>329</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>13.6</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>45.2</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>18</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>11.96</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31">
         <v>330</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>19.6</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>49.3</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>18</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>6.9</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32">
         <v>331</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>17.7</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>55.4</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>6</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>10.82</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33">
         <v>332</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>26.5</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>37.8</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>9</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>15.69</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34">
         <v>333</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>14.1</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>44.6</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>17</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>11.73</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35">
         <v>334</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>22.2</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>34.3</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>9</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>13.2</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36">
         <v>335</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>29.4</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>49.2</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>26</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>11.68</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37">
         <v>336</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>28.8</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>35.6</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>26</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>18.05</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38">
         <v>337</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>13.5</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>53.7</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>10</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>9.41</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39">
         <v>338</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>23.1</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>40.7</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>22</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>6.93</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40">
         <v>339</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>23.6</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>26.5</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>12</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>13.38</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41">
         <v>340</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>15.3</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>45.5</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>14</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>10.73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
+  </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DEB6ABA9A71C00499D5EEAE730BF8E7A" ma:contentTypeVersion="13" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="70652bcfbd156efe0e648a1b8626bdf8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3964cef-bcf6-472e-84a9-2433688d5d78" xmlns:ns3="3f8fd174-3e43-4bd4-828e-a12bdf5c173e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c609ecc9d3b3b0f82c78d4890b19a688" ns2:_="" ns3:_="">
-    <xsd:import namespace="c3964cef-bcf6-472e-84a9-2433688d5d78"/>
-    <xsd:import namespace="3f8fd174-3e43-4bd4-828e-a12bdf5c173e"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3964cef-bcf6-472e-84a9-2433688d5d78" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="5292e482-86e9-4fa8-8354-8feae1b4f4fb" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="15" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3f8fd174-3e43-4bd4-828e-a12bdf5c173e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3964cef-bcf6-472e-84a9-2433688d5d78">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{728F6414-9CCF-4252-A4C5-FBFC452712A4}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7884886-84F2-4117-8E2E-505248FBCD28}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{562A09E9-80F8-41F6-8748-A87F944F2218}"/>
 </file>